--- a/hardware/expansion-board-v4/BOM_可动性速查.xlsx
+++ b/hardware/expansion-board-v4/BOM_可动性速查.xlsx
@@ -4231,14 +4231,14 @@
         <v>73.83</v>
       </c>
       <c r="H82" t="n">
-        <v>82.31</v>
+        <v>80.31</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>U6 的去耦（3V3_DIG），现距 3.7mm；**必须跟着 U6 走**</t>
+          <t>U6 的去耦（3V3_DIG），现距 4.3mm；**必须跟着 U6 走**</t>
         </is>
       </c>
     </row>
@@ -4274,17 +4274,17 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>79.26000000000001</v>
+        <v>81.39</v>
       </c>
       <c r="H83" t="n">
-        <v>64.88</v>
+        <v>64.16</v>
       </c>
       <c r="I83" t="n">
         <v>90</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>U4 的去耦（3V3_DIG），现距 3.8mm；**必须跟着 U4 走**</t>
+          <t>U4 的去耦（3V3_DIG），现距 6.0mm；**必须跟着 U4 走**</t>
         </is>
       </c>
     </row>
@@ -4458,17 +4458,17 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>73.22</v>
+        <v>74.83</v>
       </c>
       <c r="H87" t="n">
-        <v>74</v>
+        <v>78.48</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>U7 的去耦（3V3_GNSS），现距 7.7mm；**必须跟着 U7 走**</t>
+          <t>U7 的去耦（3V3_GNSS），现距 10.3mm；**必须跟着 U7 走**</t>
         </is>
       </c>
     </row>
@@ -4504,17 +4504,17 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>73.44</v>
+        <v>74.77</v>
       </c>
       <c r="H88" t="n">
-        <v>76.41</v>
+        <v>74.91</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>U7 的去耦（3V3_GNSS），现距 8.3mm；**必须跟着 U7 走**</t>
+          <t>U7 的去耦（3V3_GNSS），现距 9.3mm；**必须跟着 U7 走**</t>
         </is>
       </c>
     </row>
@@ -4642,17 +4642,17 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>98.59</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="H91" t="n">
-        <v>80.06999999999999</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>U8 的去耦（3V3_DIG），现距 6.1mm；**必须跟着 U8 走**</t>
+          <t>U8 的去耦（3V3_DIG），现距 6.9mm；**必须跟着 U8 走**</t>
         </is>
       </c>
     </row>
@@ -4734,17 +4734,17 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>110.69</v>
+        <v>111.83</v>
       </c>
       <c r="H93" t="n">
-        <v>76.47</v>
+        <v>74.83</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>U8 的去耦（3V3_DIG），现距 6.6mm；**必须跟着 U8 走**</t>
+          <t>U8 的去耦（3V3_DIG），现距 8.3mm；**必须跟着 U8 走**</t>
         </is>
       </c>
     </row>
@@ -4780,17 +4780,17 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>108.47</v>
+        <v>105.69</v>
       </c>
       <c r="H94" t="n">
-        <v>73.75</v>
+        <v>71.61</v>
       </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>U8 的去耦（3V3_DIG），现距 6.5mm；**必须跟着 U8 走**</t>
+          <t>U8 的去耦（3V3_DIG），现距 7.5mm；**必须跟着 U8 走**</t>
         </is>
       </c>
     </row>
@@ -4826,17 +4826,17 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>104.86</v>
+        <v>102.09</v>
       </c>
       <c r="H95" t="n">
-        <v>73.75</v>
+        <v>71.61</v>
       </c>
       <c r="I95" t="n">
         <v>180</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>U8 的去耦（3V3_DIG），现距 5.3mm；**必须跟着 U8 走**</t>
+          <t>U8 的去耦（3V3_DIG），现距 7.9mm；**必须跟着 U8 走**</t>
         </is>
       </c>
     </row>
@@ -4872,17 +4872,17 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>105.26</v>
+        <v>104.43</v>
       </c>
       <c r="H96" t="n">
-        <v>84.34999999999999</v>
+        <v>86.44</v>
       </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>U8 的去耦（RP_1V1），现距 5.3mm；**必须跟着 U8 走**</t>
+          <t>U8 的去耦（RP_1V1），现距 7.4mm；**必须跟着 U8 走**</t>
         </is>
       </c>
     </row>
@@ -5473,14 +5473,14 @@
         <v>126.11</v>
       </c>
       <c r="H109" t="n">
-        <v>87.27</v>
+        <v>89.27</v>
       </c>
       <c r="I109" t="n">
         <v>0</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>U10 的去耦（3V3_DIG），现距 6.6mm；**必须跟着 U10 走**</t>
+          <t>U10 的去耦（3V3_DIG），现距 7.6mm；**必须跟着 U10 走**</t>
         </is>
       </c>
     </row>
@@ -5516,17 +5516,17 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>126.11</v>
+        <v>123.96</v>
       </c>
       <c r="H110" t="n">
-        <v>82.87</v>
+        <v>84.14</v>
       </c>
       <c r="I110" t="n">
         <v>0</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>U10 的去耦（3V3_DIG），现距 6.3mm；**必须跟着 U10 走**</t>
+          <t>U10 的去耦（3V3_DIG），现距 8.2mm；**必须跟着 U10 走**</t>
         </is>
       </c>
     </row>
@@ -5562,17 +5562,17 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>133.99</v>
+        <v>132.11</v>
       </c>
       <c r="H111" t="n">
-        <v>91.64</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>U10 的去耦（3V3_DIG），现距 7.2mm；**必须跟着 U10 走**</t>
+          <t>U10 的去耦（3V3_DIG），现距 7.7mm；**必须跟着 U10 走**</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>挪它则 3 颗去耦要跟着走：C11 C14 C16</t>
+          <t>挪它则 2 颗去耦要跟着走：C14 C16</t>
         </is>
       </c>
     </row>
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>70.98999999999999</v>
+        <v>70.06</v>
       </c>
       <c r="H142" t="n">
-        <v>64.39</v>
+        <v>66.16</v>
       </c>
       <c r="I142" t="n">
         <v>-90</v>
@@ -7080,10 +7080,10 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>66.5</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="H144" t="n">
-        <v>82.5</v>
+        <v>80.63</v>
       </c>
       <c r="I144" t="n">
         <v>0</v>
@@ -8676,38 +8676,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>上</t>
+          <t>左</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7</v>
+        <v>0.12</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>🔴 缺3根</t>
+          <t>🔴 缺2根</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>C22 C26 C27</t>
+          <t>R10 R9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>U13</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -8719,7 +8719,7 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -8731,23 +8731,23 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>R10 R9</t>
+          <t>U13</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>左</t>
+          <t>上</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -8757,24 +8757,24 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>🔴 缺2根</t>
+          <t>🔴 缺1根</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>U13</t>
+          <t>ANT1 C54</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>上</t>
+          <t>右</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -8793,26 +8793,26 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ANT1 C54</t>
+          <t>Y2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>右</t>
+          <t>下</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -8824,14 +8824,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Y2</t>
+          <t>C16</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>U13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -8840,29 +8840,29 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>🔴 缺1根</t>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>✅ 够</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>C16</t>
+          <t>U15</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -8871,44 +8871,44 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>3.27</v>
+        <v>0.14</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>🔴 缺1根</t>
+        <v>0</v>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>✅ 够</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>C28 C29</t>
+          <t>L16</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>U13</t>
+          <t>U19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>下</t>
+          <t>左</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0.19</v>
+        <v>0.96</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -8917,14 +8917,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>U15</t>
+          <t>C70 C71 C80</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>U19</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -8933,13 +8933,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.14</v>
+        <v>0.35</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
@@ -8948,29 +8948,29 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>L16</t>
+          <t>C14 U5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>U19</t>
+          <t>U6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>左</t>
+          <t>上</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.96</v>
+        <v>0.61</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
@@ -8979,14 +8979,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>C70 C71 C80</t>
+          <t>U7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>U6</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -8995,10 +8995,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.35</v>
+        <v>0.43</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -9010,14 +9010,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>C14 U5</t>
+          <t>R2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U5</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -9026,13 +9026,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.85</v>
+        <v>1.12</v>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
@@ -9041,29 +9041,29 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>C64 C65</t>
+          <t>C14</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>U5</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>上</t>
+          <t>右</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.61</v>
+        <v>1.17</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
@@ -9072,29 +9072,29 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>R26 R27</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>下</t>
+          <t>左</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.43</v>
+        <v>1.12</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
@@ -9103,29 +9103,29 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>U16</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>左</t>
+          <t>下</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
@@ -9134,14 +9134,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>C14</t>
+          <t>R18 R5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -9150,13 +9150,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1.17</v>
+        <v>1.49</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
@@ -9165,29 +9165,29 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>R26 R27</t>
+          <t>D2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>U5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>左</t>
+          <t>上</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.02</v>
+        <v>1.77</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
@@ -9196,29 +9196,29 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>C13 R3</t>
+          <t>U4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>左</t>
+          <t>下</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1.12</v>
+        <v>1.97</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
@@ -9227,14 +9227,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>C37 C63</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>U18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9243,13 +9243,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>1.22</v>
+        <v>2.88</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>R37</t>
         </is>
       </c>
     </row>
@@ -9270,17 +9270,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>下</t>
+          <t>右</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>1.33</v>
+        <v>2.63</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>R18 R5</t>
+          <t>C22</t>
         </is>
       </c>
     </row>
@@ -9301,33 +9301,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>右</t>
+          <t>下</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.49</v>
+        <v>2.59</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
           <t>✅ 够</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9336,13 +9332,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>4.42</v>
+        <v>2.47</v>
       </c>
       <c r="E23" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
@@ -9351,29 +9347,29 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>C23</t>
+          <t>C13 R3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>左</t>
+          <t>上</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>2.49</v>
+        <v>2.92</v>
       </c>
       <c r="E24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
@@ -9382,29 +9378,29 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>R1 U7</t>
+          <t>FL2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>U6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>上</t>
+          <t>右</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1.77</v>
+        <v>3.21</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
@@ -9413,29 +9409,29 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>C10</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>下</t>
+          <t>上</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>1.97</v>
+        <v>3.25</v>
       </c>
       <c r="E26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
@@ -9444,14 +9440,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>C37 C63</t>
+          <t>FL2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>U18</t>
+          <t>U13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -9463,26 +9459,22 @@
         <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>2.88</v>
+        <v>4.09</v>
       </c>
       <c r="E27" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
           <t>✅ 够</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>R37</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -9491,13 +9483,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>2.63</v>
+        <v>4.69</v>
       </c>
       <c r="E28" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
@@ -9506,14 +9498,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>C22</t>
+          <t>C10 C17 C18 U4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -9522,25 +9514,29 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D29" t="n">
-        <v>2.59</v>
+        <v>7.18</v>
       </c>
       <c r="E29" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
           <t>✅ 够</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>C29</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -9552,10 +9548,10 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>2.92</v>
+        <v>4.45</v>
       </c>
       <c r="E30" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
@@ -9564,29 +9560,29 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>FL2</t>
+          <t>C79</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>右</t>
+          <t>左</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D31" t="n">
-        <v>2.79</v>
+        <v>6.92</v>
       </c>
       <c r="E31" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
@@ -9595,149 +9591,141 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>C11</t>
+          <t>C23</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>右</t>
+          <t>上</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>5.97</v>
+        <v>5.29</v>
       </c>
       <c r="E32" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
           <t>✅ 够</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>C25</t>
-        </is>
-      </c>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>U13</t>
+          <t>U19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>上</t>
+          <t>右</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>3.25</v>
+        <v>5.29</v>
       </c>
       <c r="E33" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
           <t>✅ 够</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>FL2</t>
-        </is>
-      </c>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>U13</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>右</t>
+          <t>上</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>4.09</v>
+        <v>6.03</v>
       </c>
       <c r="E34" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
           <t>✅ 够</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>C63</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>右</t>
+          <t>上</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>4.03</v>
+        <v>4.89</v>
       </c>
       <c r="E35" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
           <t>✅ 够</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>C17 C18 U4</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>下</t>
+          <t>左</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>4.26</v>
+        <v>5.52</v>
       </c>
       <c r="E36" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
@@ -9746,29 +9734,29 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>C66</t>
+          <t>U7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>U18</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>上</t>
+          <t>下</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>4.45</v>
+        <v>4.61</v>
       </c>
       <c r="E37" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
@@ -9777,14 +9765,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>C79</t>
+          <t>R3 U6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>U19</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9793,25 +9781,29 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D38" t="n">
-        <v>5.29</v>
+        <v>7.18</v>
       </c>
       <c r="E38" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
           <t>✅ 够</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>C22</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>U19</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -9820,83 +9812,87 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D39" t="n">
-        <v>5.29</v>
+        <v>7.62</v>
       </c>
       <c r="E39" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
           <t>✅ 够</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>C25</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>上</t>
+          <t>左</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>6.03</v>
+        <v>5.89</v>
       </c>
       <c r="E40" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
           <t>✅ 够</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>C63</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>上</t>
+          <t>左</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D41" t="n">
-        <v>4.89</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
           <t>✅ 够</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>C64</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U18</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -9905,13 +9901,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>5.89</v>
+        <v>5.49</v>
       </c>
       <c r="E42" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
@@ -9923,22 +9919,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>U18</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>左</t>
+          <t>右</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>5.49</v>
+        <v>6.32</v>
       </c>
       <c r="E43" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
@@ -9981,7 +9977,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>U18</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9990,13 +9986,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>7.49</v>
+        <v>8.35</v>
       </c>
       <c r="E45" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
@@ -10008,22 +10004,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>右</t>
+          <t>下</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>8.35</v>
+        <v>7.49</v>
       </c>
       <c r="E46" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
@@ -10035,33 +10031,29 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>下</t>
+          <t>右</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>8.710000000000001</v>
+        <v>8.35</v>
       </c>
       <c r="E47" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
           <t>✅ 够</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>U6</t>
-        </is>
-      </c>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -10071,24 +10063,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>左</t>
+          <t>上</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>11.19</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="E48" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
           <t>✅ 够</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -10098,17 +10094,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>上</t>
+          <t>左</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>11.69</v>
+        <v>11.19</v>
       </c>
       <c r="E49" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>

--- a/hardware/expansion-board-v4/BOM_可动性速查.xlsx
+++ b/hardware/expansion-board-v4/BOM_可动性速查.xlsx
@@ -8,12 +8,12 @@
   </bookViews>
   <sheets>
     <sheet name="可动性速查" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="扇出通道" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="芯片净空区" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="图例" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'可动性速查'!$A$1:$J$177</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'扇出通道'!$A$1:$G$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'芯片净空区'!$A$1:$H$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -8624,16 +8624,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="5" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8649,189 +8650,209 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>需出线(根)</t>
+          <t>该边脚数</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>最大连续空隙(mm)</t>
+          <t>需落孔的脚</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>可走(根)</t>
+          <t>过孔圈数</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>够不够</t>
+          <t>需留净空(mm)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>挡路的元件</t>
+          <t>可贴近段(NC≥2)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>当前占着净空的元件</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>U13</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>左</t>
+          <t>上</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
         <v>2</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>🔴 缺2根</t>
-        </is>
+      <c r="F2" t="n">
+        <v>2.4</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>R10 R9</t>
+          <t>129.4~132.8(12个)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>C63</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>左</t>
+          <t>下</t>
         </is>
       </c>
       <c r="C3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>🔴 缺2根</t>
-        </is>
+      <c r="F3" t="n">
+        <v>2.4</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>U13</t>
+          <t>129.9~132.9(11个)、133.9~134.1(2个)</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>上</t>
+          <t>右</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>🔴 缺1根</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.4</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ANT1 C54</t>
+          <t>83.4~87.4(11个)</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>右</t>
+          <t>左</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>🔴 缺1根</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Y2</t>
+          <t>84.0~84.0(2个)、85.3~86.4(5个)</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>C64</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>U19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>下</t>
+          <t>上</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>🔴 缺1根</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>C16</t>
+          <t>144.1~145.3(6个)</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>U13</t>
+          <t>U19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -8840,22 +8861,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.4</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>U15</t>
+          <t>144.1~146.6(11个)</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>L16</t>
         </is>
       </c>
     </row>
@@ -8867,26 +8891,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>下</t>
+          <t>右</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>0.14</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.4</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>L16</t>
+          <t>80.5~81.2(6个)</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8902,20 +8929,23 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.4</v>
       </c>
       <c r="G9" t="inlineStr">
+        <is>
+          <t>80.0~82.5(7个)</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>C70 C71 C80</t>
         </is>
@@ -8929,55 +8959,61 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>下</t>
+          <t>右</t>
         </is>
       </c>
       <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="n">
         <v>1</v>
       </c>
-      <c r="D10" t="n">
-        <v>0.35</v>
-      </c>
       <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.4</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>C14 U5</t>
+          <t>63.8~67.8(9个)</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>上</t>
+          <t>左</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>0.61</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
+      <c r="F11" t="n">
+        <v>2.4</v>
       </c>
       <c r="G11" t="inlineStr">
+        <is>
+          <t>63.8~64.8(3个)、66.8~67.3(2个)</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>U7</t>
         </is>
@@ -8986,69 +9022,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>下</t>
+          <t>上</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D12" t="n">
-        <v>0.43</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.4</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>104.4~105.4(5个)、106.4~107.2(3个)</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>C22</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>左</t>
+          <t>下</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>1.12</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.4</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>C14</t>
+          <t>103.6~103.8(2个)、104.8~105.4(3个)</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>C29</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -9057,29 +9099,32 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>1.17</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.4</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>R26 R27</t>
+          <t>76.4~77.2(3个)</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>C25</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -9088,91 +9133,100 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>1.12</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.4</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>80.0~80.8(3个)</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>C23</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>下</t>
+          <t>上</t>
         </is>
       </c>
       <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="D16" t="n">
-        <v>1.33</v>
-      </c>
       <c r="E16" t="n">
-        <v>4</v>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.6</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>R18 R5</t>
+          <t>75.9~76.4(2个)</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>右</t>
+          <t>下</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1.49</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.6</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>74.9~75.9(3个)</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>U5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>U6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -9181,29 +9235,32 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1.77</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.6</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>69.9~70.9(3个)</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>U7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -9212,29 +9269,32 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.6</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>C37 C63</t>
+          <t>69.4~70.9(4个)</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>U18</t>
+          <t>U6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9243,87 +9303,100 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>2.88</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>9</v>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.6</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>R37</t>
+          <t>81.8~82.2(2个)</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>C10</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>右</t>
+          <t>左</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>2.63</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>8</v>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.6</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>C22</t>
+          <t>82.2~83.2(3个)</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>C13 R3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>下</t>
+          <t>右</t>
         </is>
       </c>
       <c r="C22" t="n">
+        <v>9</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
         <v>1</v>
       </c>
-      <c r="D22" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="E22" t="n">
-        <v>8</v>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>69.6~74.0(5个)</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9332,789 +9405,30 @@
         </is>
       </c>
       <c r="C23" t="n">
+        <v>9</v>
+      </c>
+      <c r="D23" t="n">
         <v>1</v>
       </c>
-      <c r="D23" t="n">
-        <v>2.47</v>
-      </c>
       <c r="E23" t="n">
-        <v>8</v>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.6</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>C13 R3</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>U14</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>上</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E24" t="n">
-        <v>9</v>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>FL2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>U6</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>右</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="E25" t="n">
-        <v>10</v>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>C10</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>U13</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>上</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="E26" t="n">
-        <v>10</v>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>FL2</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>U13</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>右</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>3</v>
-      </c>
-      <c r="D27" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="E27" t="n">
-        <v>13</v>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>U7</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>右</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>3</v>
-      </c>
-      <c r="D28" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="E28" t="n">
-        <v>15</v>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>C10 C17 C18 U4</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>U8</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>下</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>11</v>
-      </c>
-      <c r="D29" t="n">
-        <v>7.18</v>
-      </c>
-      <c r="E29" t="n">
-        <v>23</v>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>C29</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>U18</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>上</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="E30" t="n">
-        <v>14</v>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>C79</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>U8</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>左</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>10</v>
-      </c>
-      <c r="D31" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="E31" t="n">
-        <v>23</v>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>C23</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>U19</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>上</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>3</v>
-      </c>
-      <c r="D32" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="E32" t="n">
-        <v>17</v>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>U19</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>右</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>3</v>
-      </c>
-      <c r="D33" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="E33" t="n">
-        <v>17</v>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>U10</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>上</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>5</v>
-      </c>
-      <c r="D34" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="E34" t="n">
-        <v>20</v>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>C63</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>U4</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>上</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="E35" t="n">
-        <v>16</v>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>U4</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>左</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>3</v>
-      </c>
-      <c r="D36" t="n">
-        <v>5.52</v>
-      </c>
-      <c r="E36" t="n">
-        <v>18</v>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>U7</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>U7</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>下</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="E37" t="n">
-        <v>15</v>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>R3 U6</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>U8</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>上</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>8</v>
-      </c>
-      <c r="D38" t="n">
-        <v>7.18</v>
-      </c>
-      <c r="E38" t="n">
-        <v>23</v>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>C22</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>U8</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>右</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>10</v>
-      </c>
-      <c r="D39" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="E39" t="n">
-        <v>25</v>
-      </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>C25</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>U9</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>左</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>2</v>
-      </c>
-      <c r="D40" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="E40" t="n">
-        <v>19</v>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>U10</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>左</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>8</v>
-      </c>
-      <c r="D41" t="n">
-        <v>8.029999999999999</v>
-      </c>
-      <c r="E41" t="n">
-        <v>26</v>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>C64</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>U18</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>左</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="E42" t="n">
-        <v>18</v>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>U4</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>右</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" t="n">
-        <v>6.32</v>
-      </c>
-      <c r="E43" t="n">
-        <v>21</v>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>U9</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>上</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" t="n">
-        <v>6.88</v>
-      </c>
-      <c r="E44" t="n">
-        <v>22</v>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>C24</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>U10</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>下</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>3</v>
-      </c>
-      <c r="D45" t="n">
-        <v>8.35</v>
-      </c>
-      <c r="E45" t="n">
-        <v>27</v>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>U18</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>下</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="E46" t="n">
-        <v>24</v>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>U10</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>右</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>2</v>
-      </c>
-      <c r="D47" t="n">
-        <v>8.35</v>
-      </c>
-      <c r="E47" t="n">
-        <v>27</v>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>U7</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>上</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" t="n">
-        <v>9.630000000000001</v>
-      </c>
-      <c r="E48" t="n">
-        <v>32</v>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>U7</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>左</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" t="n">
-        <v>11.19</v>
-      </c>
-      <c r="E49" t="n">
-        <v>37</v>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>✅ 够</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+          <t>71.8~78.4(7个)</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G49"/>
+  <autoFilter ref="A1:H23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10125,7 +9439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10204,56 +9518,176 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>改完布局跑这三条验收：</t>
+          <t>改完布局按顺序跑这四条：</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tools/frozen_report.py F</t>
+          <t>1. tools/keepout_report.py</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>看有没有元件占了芯片的扇出净空区</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>最关键，占了就布不出线</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tools/fanout_channel.py</t>
-        </is>
-      </c>
+          <t>2. tools/frozen_report.py F</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>看有没有动到 🔴 钉死的件</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>tools/check_silk.py F</t>
-        </is>
-      </c>
+          <t>3. tools/check_silk.py F</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>丝印：压焊盘 / 重叠 / 离元件太远</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kicad-cli pcb drc --severity-error</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>扇出通道口径：芯片边缘往外 2.0mm 的带子，每根线按 0.15 线宽 + 0.15 间距 = 0.30mm 估</t>
+          <t>4. kicad-cli pcb drc --severity-error</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>必须 0 条</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>（去耦跟丢了跑 tools/apply_keepout.py，会自动挪出净空区并保持最近）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>「需出线」只数信号脚，GND/电源不算（那些就近打过孔下地）</t>
+          <t>净空区是怎么算出来的（依据 v3 已打样板的实测）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>U14 是 AD8313 备用检波位、与 U13 二选一默认不贴，已从「挡路」里排除</t>
+          <t>真实扇出方式</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>引脚 → 0.15mm 短线走 0.5~1mm → 就近打过孔下内层，表层不横穿</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>v3 实测</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>U8 周围过孔 37 个、距边界 0.12~3.73mm，那一圈里一个元件都没有</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>净空公式</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>圈数 = ceil(该边脚数 / (边长/0.8))，净空 = 0.8 + 圈数x0.8，夹 1.2~3.2mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0.8mm 哪来的</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0.305 孔 + 0.6 盘 + 0.2 间距（孔径取自实测 Gerber）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>不算进去的脚</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>① 连续 ≥2 个的 NC 段  ② 电源/地脚——它们走粗线直连或就近下地，不排过孔阵列</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>所以 L16/C71/C80 贴着 SY6970 的 LX/BST/PMID 是对的，不算违规</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>其它口径</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>走线/过孔</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>实测生产 Gerber：走线 0.20mm、过孔孔径 0.305mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>U14</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>AD8313 备用检波位、与 U13 二选一默认不贴，已从「挡路」里排除</t>
         </is>
       </c>
     </row>

--- a/hardware/expansion-board-v4/BOM_可动性速查.xlsx
+++ b/hardware/expansion-board-v4/BOM_可动性速查.xlsx
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>85.45999999999999</v>
+        <v>79.16</v>
       </c>
       <c r="H2" t="n">
         <v>57.75</v>
@@ -558,7 +558,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>板载 1090 IFA 天线，44mm 总长是调过的；周围六层禁铺区跟着它走</t>
+          <t>板载1090 IFA预研几何：52.0mm画长/53.5mm外包络；六层禁铜区跟随封装，尚未实板调准</t>
         </is>
       </c>
     </row>
@@ -732,13 +732,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>98.3</v>
+        <v>96.77</v>
       </c>
       <c r="H6" t="n">
-        <v>62.87</v>
+        <v>61.34</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -3262,13 +3262,13 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>86.2</v>
+        <v>79.17</v>
       </c>
       <c r="H61" t="n">
-        <v>62.87</v>
+        <v>63.64</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>93.8</v>
+        <v>84.17</v>
       </c>
       <c r="H62" t="n">
-        <v>62.87</v>
+        <v>63.64</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>90</v>
+        <v>81.67</v>
       </c>
       <c r="H63" t="n">
         <v>62.87</v>
@@ -4274,17 +4274,17 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>81.39</v>
+        <v>80.8</v>
       </c>
       <c r="H83" t="n">
-        <v>64.16</v>
+        <v>67</v>
       </c>
       <c r="I83" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>U4 的去耦（3V3_DIG），现距 6.0mm；**必须跟着 U4 走**</t>
+          <t>U4 的去耦（3V3_DIG），现距 5.2mm；**必须跟着 U4 走**</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>挪它则 2 颗去耦要跟着走：C14 C16</t>
+          <t>挪它则 3 颗去耦要跟着走：C11 C14 C16</t>
         </is>
       </c>
     </row>
@@ -8979,9 +8979,9 @@
           <t>63.8~67.8(9个)</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>C11 ZP1 ZS1</t>
         </is>
       </c>
     </row>
